--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484830_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484830_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.4793</v>
+        <v>4.9019</v>
       </c>
       <c r="E2" t="n">
-        <v>5.3649</v>
+        <v>5.1314</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1144</v>
+        <v>-0.2295</v>
       </c>
       <c r="G2" t="n">
         <v>2.9257</v>
@@ -610,13 +610,13 @@
         <v>3.2079</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.9064</v>
+        <v>-1.4838</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0181</v>
+        <v>-0.2154</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.9245</v>
+        <v>-1.2684</v>
       </c>
       <c r="V2" t="n">
         <v>3.2713</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.8322</v>
+        <v>4.0149</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3009</v>
+        <v>2.4571</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5313</v>
+        <v>1.5578</v>
       </c>
       <c r="G3" t="n">
         <v>0.8522</v>
@@ -688,13 +688,13 @@
         <v>2.6418</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7372</v>
+        <v>-0.5545</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3498</v>
+        <v>-0.1936</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3873</v>
+        <v>-0.3609</v>
       </c>
       <c r="V3" t="n">
         <v>2.2076</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. ALAMINOS HERNANDEZ</t>
+          <t>M. MARTIN MARTINEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.224</v>
+        <v>1.6688</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8287</v>
+        <v>1.4101</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3953</v>
+        <v>0.2587</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5901</v>
+        <v>0.3742</v>
       </c>
       <c r="H5" t="n">
-        <v>2.1529</v>
+        <v>0.0517</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5628</v>
+        <v>0.3225</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3578</v>
+        <v>1.5169</v>
       </c>
       <c r="K5" t="n">
-        <v>2.0074</v>
+        <v>0.0689</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6496</v>
+        <v>1.4481</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2324</v>
+        <v>-1.1428</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1456</v>
+        <v>-0.0172</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0868</v>
+        <v>-1.1256</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3774</v>
+        <v>1.6983</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5661</v>
+        <v>1.6983</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1358</v>
+        <v>-0.4037</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4144</v>
+        <v>-0.1069</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2786</v>
+        <v>-0.2968</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1245</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1245</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. MARTIN MARTINEZ</t>
+          <t>I. ALAMINOS HERNANDEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.106</v>
+        <v>1.1169</v>
       </c>
       <c r="E6" t="n">
-        <v>1.059</v>
+        <v>0.5364</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0471</v>
+        <v>0.5805</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3742</v>
+        <v>1.5901</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0517</v>
+        <v>2.1529</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3225</v>
+        <v>-0.5628</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5169</v>
+        <v>1.3578</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0689</v>
+        <v>2.0074</v>
       </c>
       <c r="L6" t="n">
-        <v>1.4481</v>
+        <v>-0.6496</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1428</v>
+        <v>0.2324</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0172</v>
+        <v>0.1456</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.1256</v>
+        <v>0.0868</v>
       </c>
       <c r="P6" t="n">
-        <v>1.6983</v>
+        <v>-0.3774</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6983</v>
+        <v>0.5661</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9664</v>
+        <v>0.0287</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.458</v>
+        <v>0.1221</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5085</v>
+        <v>-0.0934</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.1245</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.1245</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2638</v>
+        <v>0.5645</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1341</v>
+        <v>0.0608</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3979</v>
+        <v>0.5037</v>
       </c>
       <c r="G7" t="n">
         <v>0.5776</v>
@@ -1000,13 +1000,13 @@
         <v>0.3774</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5667</v>
+        <v>-0.266</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1764</v>
+        <v>0.0185</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3903</v>
+        <v>-0.2845</v>
       </c>
       <c r="V7" t="n">
         <v>-0.1245</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.696</v>
+        <v>-0.4398</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9234</v>
+        <v>-0.826</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2275</v>
+        <v>0.3862</v>
       </c>
       <c r="G8" t="n">
         <v>1.5866</v>
@@ -1078,13 +1078,13 @@
         <v>0.7548</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.6295</v>
+        <v>-1.3733</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3404</v>
+        <v>-0.243</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.2891</v>
+        <v>-1.1304</v>
       </c>
       <c r="V8" t="n">
         <v>0.4791</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.455</v>
+        <v>-1.4285</v>
       </c>
       <c r="E9" t="n">
         <v>-0.8048</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6502</v>
+        <v>-0.6237</v>
       </c>
       <c r="G9" t="n">
         <v>-1.4138</v>
@@ -1156,13 +1156,13 @@
         <v>0.1887</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2299</v>
+        <v>-0.2034</v>
       </c>
       <c r="T9" t="n">
         <v>-0.1764</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0535</v>
+        <v>-0.027</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. QUERALT-LORTZING VILLANUEVA</t>
+          <t>J. GARCIA NAVEA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6638</v>
+        <v>-1.6248</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8031</v>
+        <v>-0.9277</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8607</v>
+        <v>-0.6971000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4601</v>
+        <v>0.7228</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.6012</v>
+        <v>-1.2123</v>
       </c>
       <c r="I10" t="n">
-        <v>1.1411</v>
+        <v>1.9351</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.4763</v>
+        <v>2.7226</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.5997</v>
+        <v>0.1385</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1234</v>
+        <v>2.5841</v>
       </c>
       <c r="M10" t="n">
-        <v>1.0162</v>
+        <v>-1.9998</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0015</v>
+        <v>-1.3507</v>
       </c>
       <c r="O10" t="n">
-        <v>1.0177</v>
+        <v>-0.649</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-3.3966</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1322</v>
+        <v>-5.661</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1322</v>
+        <v>2.2644</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4868</v>
+        <v>-0.8188</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8999</v>
+        <v>-0.4797</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4132</v>
+        <v>-0.3391</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.6905</v>
+        <v>1.8678</v>
       </c>
       <c r="W10" t="n">
-        <v>0.9054</v>
+        <v>2.4904</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.5959</v>
+        <v>-0.6226</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. GARCIA NAVEA</t>
+          <t>A. QUERALT-LORTZING VILLANUEVA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7823</v>
+        <v>-2.6369</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3762</v>
+        <v>-1.4851</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4061</v>
+        <v>-1.1517</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7228</v>
+        <v>-0.4601</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.2123</v>
+        <v>-1.6012</v>
       </c>
       <c r="I11" t="n">
-        <v>1.9351</v>
+        <v>1.1411</v>
       </c>
       <c r="J11" t="n">
-        <v>2.7226</v>
+        <v>-1.4763</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1385</v>
+        <v>-1.5997</v>
       </c>
       <c r="L11" t="n">
-        <v>2.5841</v>
+        <v>0.1234</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.9998</v>
+        <v>1.0162</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.3507</v>
+        <v>-0.0015</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.649</v>
+        <v>1.0177</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.3966</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-5.661</v>
+        <v>-1.1322</v>
       </c>
       <c r="R11" t="n">
-        <v>2.2644</v>
+        <v>1.1322</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9764</v>
+        <v>-0.4863</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9283</v>
+        <v>0.2179</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0481</v>
+        <v>-0.7042</v>
       </c>
       <c r="V11" t="n">
-        <v>1.8678</v>
+        <v>-1.6905</v>
       </c>
       <c r="W11" t="n">
-        <v>2.4904</v>
+        <v>0.9054</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.6226</v>
+        <v>-2.5959</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.4583</v>
+        <v>-3.1517</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.0335</v>
+        <v>0.2202</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.4248</v>
+        <v>-3.3719</v>
       </c>
       <c r="G12" t="n">
         <v>1.3038</v>
@@ -1390,13 +1390,13 @@
         <v>0.5661</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.7247</v>
+        <v>-1.4181</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.393</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.078</v>
+        <v>-1.0251</v>
       </c>
       <c r="V12" t="n">
         <v>-3.4148</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-11.0362</v>
+        <v>-10.8775</v>
       </c>
       <c r="E13" t="n">
         <v>-7.0909</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.9453</v>
+        <v>-3.7866</v>
       </c>
       <c r="G13" t="n">
         <v>-4.2404</v>
@@ -1468,13 +1468,13 @@
         <v>2.6418</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.041</v>
+        <v>-1.8823</v>
       </c>
       <c r="T13" t="n">
         <v>-0.4086</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.6324</v>
+        <v>-1.4737</v>
       </c>
       <c r="V13" t="n">
         <v>-2.4904</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.301499999999997</v>
+        <v>-6.007399999999997</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2722999999999978</v>
+        <v>0.5663</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.573599999999999</v>
+        <v>-6.5736</v>
       </c>
       <c r="G14" t="n">
-        <v>5.703500000000001</v>
+        <v>5.703499999999999</v>
       </c>
       <c r="H14" t="n">
         <v>-4.147699999999999</v>
@@ -1522,13 +1522,13 @@
         <v>11.1067</v>
       </c>
       <c r="K14" t="n">
-        <v>1.8</v>
+        <v>1.799999999999999</v>
       </c>
       <c r="L14" t="n">
         <v>9.306799999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-5.4031</v>
+        <v>-5.403100000000001</v>
       </c>
       <c r="N14" t="n">
         <v>-5.9474</v>
@@ -1546,13 +1546,13 @@
         <v>16.0395</v>
       </c>
       <c r="S14" t="n">
-        <v>-9.1556</v>
+        <v>-8.861499999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.1522</v>
+        <v>-1.8581</v>
       </c>
       <c r="U14" t="n">
-        <v>-7.003500000000001</v>
+        <v>-7.0035</v>
       </c>
       <c r="V14" t="n">
         <v>-0.01890000000000081</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>O. CAMARA</t>
+          <t>M. VARELA BARCIA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.1684</v>
+        <v>3.3987</v>
       </c>
       <c r="E15" t="n">
-        <v>5.5861</v>
+        <v>1.7467</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.4177</v>
+        <v>1.652</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0188</v>
+        <v>-2.5446</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6096</v>
+        <v>-1.397</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5909</v>
+        <v>-1.1476</v>
       </c>
       <c r="J15" t="n">
-        <v>1.2542</v>
+        <v>-0.6219</v>
       </c>
       <c r="K15" t="n">
-        <v>1.1308</v>
+        <v>-1.314</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1234</v>
+        <v>0.6922</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.2354</v>
+        <v>-1.9227</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5212</v>
+        <v>-0.0829</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.7143</v>
+        <v>-1.8398</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3774</v>
+        <v>0.7548</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9435</v>
+        <v>-2.0757</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3209</v>
+        <v>2.8305</v>
       </c>
       <c r="S15" t="n">
-        <v>4.3759</v>
+        <v>2.0755</v>
       </c>
       <c r="T15" t="n">
-        <v>4.0302</v>
+        <v>1.3312</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3457</v>
+        <v>0.7443</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.6036</v>
+        <v>3.113</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2452</v>
+        <v>3.113</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.8488</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. VARELA BARCIA</t>
+          <t>O. CAMARA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.7198</v>
+        <v>2.1488</v>
       </c>
       <c r="E16" t="n">
-        <v>2.039</v>
+        <v>3.54</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6809</v>
+        <v>-1.3912</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.5446</v>
+        <v>0.0188</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.397</v>
+        <v>0.6096</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.1476</v>
+        <v>-0.5909</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.6219</v>
+        <v>1.2542</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.314</v>
+        <v>1.1308</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6922</v>
+        <v>0.1234</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.9227</v>
+        <v>-1.2354</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0829</v>
+        <v>-0.5212</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.8398</v>
+        <v>-0.7143</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7548</v>
+        <v>0.3774</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.0757</v>
+        <v>-0.9435</v>
       </c>
       <c r="R16" t="n">
-        <v>2.8305</v>
+        <v>1.3209</v>
       </c>
       <c r="S16" t="n">
-        <v>2.3966</v>
+        <v>2.3562</v>
       </c>
       <c r="T16" t="n">
-        <v>1.6235</v>
+        <v>1.9841</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7731</v>
+        <v>0.3721</v>
       </c>
       <c r="V16" t="n">
-        <v>3.113</v>
+        <v>-0.6036</v>
       </c>
       <c r="W16" t="n">
-        <v>3.113</v>
+        <v>1.2452</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.8488</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.0052</v>
+        <v>2.0382</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3335</v>
+        <v>-1.113</v>
       </c>
       <c r="F17" t="n">
-        <v>3.3387</v>
+        <v>3.1512</v>
       </c>
       <c r="G17" t="n">
         <v>-0.9025</v>
@@ -1780,13 +1780,13 @@
         <v>1.887</v>
       </c>
       <c r="S17" t="n">
-        <v>2.8322</v>
+        <v>1.8652</v>
       </c>
       <c r="T17" t="n">
-        <v>1.9639</v>
+        <v>1.1844</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8683</v>
+        <v>0.6808</v>
       </c>
       <c r="V17" t="n">
         <v>1.2642</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. GONZALEZ DIAZ</t>
+          <t>T. BOUNDI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.8256</v>
+        <v>1.4078</v>
       </c>
       <c r="E18" t="n">
-        <v>3.4342</v>
+        <v>1.2892</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.6086</v>
+        <v>0.1186</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5814</v>
+        <v>1.4291</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.1676</v>
+        <v>1.3077</v>
       </c>
       <c r="I18" t="n">
-        <v>1.749</v>
+        <v>0.1214</v>
       </c>
       <c r="J18" t="n">
-        <v>2.938</v>
+        <v>2.5449</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.3694</v>
+        <v>1.1465</v>
       </c>
       <c r="L18" t="n">
-        <v>3.3074</v>
+        <v>1.3984</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.3566</v>
+        <v>-1.1158</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7982</v>
+        <v>0.1612</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.5584</v>
+        <v>-1.277</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1887</v>
+        <v>1.1322</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.887</v>
+        <v>-1.1322</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0757</v>
+        <v>2.2644</v>
       </c>
       <c r="S18" t="n">
-        <v>1.3573</v>
+        <v>0.4315</v>
       </c>
       <c r="T18" t="n">
-        <v>1.138</v>
+        <v>0.2163</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2193</v>
+        <v>0.2152</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3018</v>
+        <v>-1.585</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2452</v>
+        <v>-0.3398</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.547</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T. BOUNDI</t>
+          <t>C. GONZALEZ DIAZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.6147</v>
+        <v>1.3746</v>
       </c>
       <c r="E19" t="n">
-        <v>1.679</v>
+        <v>3.1419</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.06419999999999999</v>
+        <v>-1.7673</v>
       </c>
       <c r="G19" t="n">
-        <v>1.4291</v>
+        <v>0.5814</v>
       </c>
       <c r="H19" t="n">
-        <v>1.3077</v>
+        <v>-1.1676</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1214</v>
+        <v>1.749</v>
       </c>
       <c r="J19" t="n">
-        <v>2.5449</v>
+        <v>2.938</v>
       </c>
       <c r="K19" t="n">
-        <v>1.1465</v>
+        <v>-0.3694</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3984</v>
+        <v>3.3074</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.1158</v>
+        <v>-2.3566</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1612</v>
+        <v>-0.7982</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.277</v>
+        <v>-1.5584</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1322</v>
+        <v>0.1887</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1322</v>
+        <v>-1.887</v>
       </c>
       <c r="R19" t="n">
-        <v>2.2644</v>
+        <v>2.0757</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6384</v>
+        <v>0.9063</v>
       </c>
       <c r="T19" t="n">
-        <v>0.606</v>
+        <v>0.8457</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0324</v>
+        <v>0.0606</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.585</v>
+        <v>-0.3018</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3398</v>
+        <v>1.2452</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2452</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.3346</v>
+        <v>1.0687</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1282</v>
+        <v>0.8359</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2063</v>
+        <v>0.2328</v>
       </c>
       <c r="G20" t="n">
         <v>0.7849</v>
@@ -2014,13 +2014,13 @@
         <v>0.1887</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3609</v>
+        <v>0.0951</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4732</v>
+        <v>0.1809</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1123</v>
+        <v>-0.0858</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,10 +2047,10 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1598</v>
+        <v>0.912</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.414</v>
+        <v>0.6578000000000001</v>
       </c>
       <c r="F21" t="n">
         <v>0.2542</v>
@@ -2092,10 +2092,10 @@
         <v>2.2644</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5661</v>
+        <v>0.5057</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6343</v>
+        <v>0.4374</v>
       </c>
       <c r="U21" t="n">
         <v>0.0682</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. CABALLERO ROMERO</t>
+          <t>P. GOMEZ GARCIA-GUTIERREZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.8074</v>
+        <v>0.5816</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.726</v>
+        <v>0.7774</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0814</v>
+        <v>-0.1958</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.6898</v>
+        <v>-0.0185</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0814</v>
+        <v>1.1637</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6084000000000001</v>
+        <v>-1.1823</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6084000000000001</v>
+        <v>1.3473</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>1.231</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6084000000000001</v>
+        <v>0.1163</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.0814</v>
+        <v>-1.3659</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0814</v>
+        <v>-0.0673</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>-1.2986</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-0.5661</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-3.0192</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.4531</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1176</v>
+        <v>0.5436</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1176</v>
+        <v>0.2796</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>0.264</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.6226</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.1696</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P. GOMEZ GARCIA-GUTIERREZ</t>
+          <t>A. CABALLERO ROMERO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.0531</v>
+        <v>-0.71</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.4893</v>
+        <v>-0.6286</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5638</v>
+        <v>-0.0814</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.0185</v>
+        <v>-0.6898</v>
       </c>
       <c r="H23" t="n">
-        <v>1.1637</v>
+        <v>-0.0814</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.1823</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>1.3473</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>1.231</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1163</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.3659</v>
+        <v>-0.0814</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0673</v>
+        <v>-0.0814</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.2986</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.5661</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.0192</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.4531</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.091</v>
+        <v>-0.0201</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9871</v>
+        <v>-0.0201</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.104</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>0.6226</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>2.1696</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.547</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.9087</v>
+        <v>-2.3867</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.4429</v>
+        <v>-1.0532</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.4658</v>
+        <v>-1.3335</v>
       </c>
       <c r="G24" t="n">
         <v>0.4248</v>
@@ -2326,13 +2326,13 @@
         <v>0.3774</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2769</v>
+        <v>0.2451</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2352</v>
+        <v>0.1546</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0417</v>
+        <v>0.0905</v>
       </c>
       <c r="V24" t="n">
         <v>-1.547</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.4379</v>
+        <v>-2.8827</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.8871</v>
+        <v>-2.6204</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.5508</v>
+        <v>-0.2622</v>
       </c>
       <c r="G25" t="n">
         <v>-3.8725</v>
@@ -2404,13 +2404,13 @@
         <v>3.2079</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7542</v>
+        <v>0.8011</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8571</v>
+        <v>0.4095</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1029</v>
+        <v>0.3916</v>
       </c>
       <c r="V25" t="n">
         <v>-0.9434</v>
@@ -2437,25 +2437,25 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>6.3014</v>
+        <v>6.950999999999999</v>
       </c>
       <c r="E26" t="n">
         <v>6.573699999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.2722000000000002</v>
+        <v>0.3774000000000002</v>
       </c>
       <c r="G26" t="n">
-        <v>-5.7035</v>
+        <v>-5.703499999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>4.147600000000001</v>
+        <v>4.1476</v>
       </c>
       <c r="I26" t="n">
-        <v>-9.851299999999998</v>
+        <v>-9.8513</v>
       </c>
       <c r="J26" t="n">
-        <v>5.4029</v>
+        <v>5.402900000000001</v>
       </c>
       <c r="K26" t="n">
         <v>5.9474</v>
@@ -2473,7 +2473,7 @@
         <v>-9.306799999999999</v>
       </c>
       <c r="P26" t="n">
-        <v>2.8305</v>
+        <v>2.830500000000001</v>
       </c>
       <c r="Q26" t="n">
         <v>-16.0395</v>
@@ -2482,13 +2482,13 @@
         <v>18.87</v>
       </c>
       <c r="S26" t="n">
-        <v>9.1555</v>
+        <v>9.805200000000001</v>
       </c>
       <c r="T26" t="n">
-        <v>7.003499999999999</v>
+        <v>7.003599999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>2.1519</v>
+        <v>2.8015</v>
       </c>
       <c r="V26" t="n">
         <v>0.01900000000000035</v>
